--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127795594</v>
       </c>
       <c r="B4" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127795776</v>
       </c>
       <c r="B5" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127795165</v>
       </c>
       <c r="B2" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127795120</v>
       </c>
       <c r="B3" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127795594</v>
+        <v>127795776</v>
       </c>
       <c r="B4" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469193</v>
+        <v>469179</v>
       </c>
       <c r="R4" t="n">
-        <v>6867295</v>
+        <v>6867297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127795776</v>
+        <v>127795594</v>
       </c>
       <c r="B5" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469179</v>
+        <v>469193</v>
       </c>
       <c r="R5" t="n">
-        <v>6867297</v>
+        <v>6867295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>127795817</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127795470</v>
+        <v>127795070</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>79055</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469186</v>
+        <v>469126</v>
       </c>
       <c r="R7" t="n">
-        <v>6867314</v>
+        <v>6867219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127795070</v>
+        <v>127795470</v>
       </c>
       <c r="B8" t="n">
-        <v>79052</v>
+        <v>80126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469126</v>
+        <v>469186</v>
       </c>
       <c r="R8" t="n">
-        <v>6867219</v>
+        <v>6867314</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>127795216</v>
       </c>
       <c r="B9" t="n">
-        <v>79052</v>
+        <v>79055</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127795165</v>
       </c>
       <c r="B2" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127795120</v>
       </c>
       <c r="B3" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127795776</v>
+        <v>127795594</v>
       </c>
       <c r="B4" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469179</v>
+        <v>469193</v>
       </c>
       <c r="R4" t="n">
-        <v>6867297</v>
+        <v>6867295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127795594</v>
+        <v>127795776</v>
       </c>
       <c r="B5" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469193</v>
+        <v>469179</v>
       </c>
       <c r="R5" t="n">
-        <v>6867295</v>
+        <v>6867297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>127795817</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127795070</v>
       </c>
       <c r="B7" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127795470</v>
       </c>
       <c r="B8" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127795216</v>
       </c>
       <c r="B9" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127795594</v>
       </c>
       <c r="B4" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127795776</v>
       </c>
       <c r="B5" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127795070</v>
+        <v>127795470</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469126</v>
+        <v>469186</v>
       </c>
       <c r="R7" t="n">
-        <v>6867219</v>
+        <v>6867314</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127795470</v>
+        <v>127795070</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469186</v>
+        <v>469126</v>
       </c>
       <c r="R8" t="n">
-        <v>6867314</v>
+        <v>6867219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127795470</v>
+        <v>127795070</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>79061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469186</v>
+        <v>469126</v>
       </c>
       <c r="R7" t="n">
-        <v>6867314</v>
+        <v>6867219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127795070</v>
+        <v>127795470</v>
       </c>
       <c r="B8" t="n">
-        <v>79061</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469126</v>
+        <v>469186</v>
       </c>
       <c r="R8" t="n">
-        <v>6867219</v>
+        <v>6867314</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127795594</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127795776</v>
       </c>
       <c r="B5" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>127795594</v>
       </c>
       <c r="B4" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127795776</v>
       </c>
       <c r="B5" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127795070</v>
+        <v>127795470</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469126</v>
+        <v>469186</v>
       </c>
       <c r="R7" t="n">
-        <v>6867219</v>
+        <v>6867314</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127795470</v>
+        <v>127795070</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>79061</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469186</v>
+        <v>469126</v>
       </c>
       <c r="R8" t="n">
-        <v>6867314</v>
+        <v>6867219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127795594</v>
+        <v>127795776</v>
       </c>
       <c r="B4" t="n">
         <v>91352</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469193</v>
+        <v>469179</v>
       </c>
       <c r="R4" t="n">
-        <v>6867295</v>
+        <v>6867297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127795776</v>
+        <v>127795594</v>
       </c>
       <c r="B5" t="n">
         <v>91352</v>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469179</v>
+        <v>469193</v>
       </c>
       <c r="R5" t="n">
-        <v>6867297</v>
+        <v>6867295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127795165</v>
       </c>
       <c r="B2" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127795120</v>
       </c>
       <c r="B3" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127795776</v>
+        <v>127795594</v>
       </c>
       <c r="B4" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469179</v>
+        <v>469193</v>
       </c>
       <c r="R4" t="n">
-        <v>6867297</v>
+        <v>6867295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127795594</v>
+        <v>127795776</v>
       </c>
       <c r="B5" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469193</v>
+        <v>469179</v>
       </c>
       <c r="R5" t="n">
-        <v>6867295</v>
+        <v>6867297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>127795817</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>127795070</v>
       </c>
       <c r="B7" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>127795470</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>127795216</v>
       </c>
       <c r="B9" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127795165</v>
       </c>
       <c r="B2" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127795120</v>
       </c>
       <c r="B3" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127795594</v>
+        <v>127795776</v>
       </c>
       <c r="B4" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469193</v>
+        <v>469179</v>
       </c>
       <c r="R4" t="n">
-        <v>6867295</v>
+        <v>6867297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127795776</v>
+        <v>127795594</v>
       </c>
       <c r="B5" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469179</v>
+        <v>469193</v>
       </c>
       <c r="R5" t="n">
-        <v>6867297</v>
+        <v>6867295</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
         <v>127795817</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127795070</v>
+        <v>127795470</v>
       </c>
       <c r="B7" t="n">
-        <v>79064</v>
+        <v>80188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469126</v>
+        <v>469186</v>
       </c>
       <c r="R7" t="n">
-        <v>6867219</v>
+        <v>6867314</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127795470</v>
+        <v>127795070</v>
       </c>
       <c r="B8" t="n">
-        <v>80135</v>
+        <v>79115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469186</v>
+        <v>469126</v>
       </c>
       <c r="R8" t="n">
-        <v>6867314</v>
+        <v>6867219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>127795216</v>
       </c>
       <c r="B9" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127795776</v>
+        <v>127795594</v>
       </c>
       <c r="B4" t="n">
         <v>91452</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469179</v>
+        <v>469193</v>
       </c>
       <c r="R4" t="n">
-        <v>6867297</v>
+        <v>6867295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127795594</v>
+        <v>127795776</v>
       </c>
       <c r="B5" t="n">
         <v>91452</v>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469193</v>
+        <v>469179</v>
       </c>
       <c r="R5" t="n">
-        <v>6867295</v>
+        <v>6867297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127795165</v>
+        <v>127795070</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469146</v>
+        <v>469126</v>
       </c>
       <c r="R2" t="n">
-        <v>6867259</v>
+        <v>6867219</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +775,7 @@
         <v>127795120</v>
       </c>
       <c r="B3" t="n">
-        <v>79115</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127795594</v>
+        <v>127795165</v>
       </c>
       <c r="B4" t="n">
-        <v>91452</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469193</v>
+        <v>469146</v>
       </c>
       <c r="R4" t="n">
-        <v>6867295</v>
+        <v>6867259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127795776</v>
+        <v>127795216</v>
       </c>
       <c r="B5" t="n">
-        <v>91452</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469179</v>
+        <v>469146</v>
       </c>
       <c r="R5" t="n">
-        <v>6867297</v>
+        <v>6867271</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127795817</v>
+        <v>127795594</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469179</v>
+        <v>469193</v>
       </c>
       <c r="R6" t="n">
-        <v>6867255</v>
+        <v>6867295</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127795470</v>
+        <v>127795776</v>
       </c>
       <c r="B7" t="n">
-        <v>80188</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469186</v>
+        <v>469179</v>
       </c>
       <c r="R7" t="n">
-        <v>6867314</v>
+        <v>6867297</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Två meter ovanför marken i sumpskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127795070</v>
+        <v>127795470</v>
       </c>
       <c r="B8" t="n">
-        <v>79115</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469126</v>
+        <v>469186</v>
       </c>
       <c r="R8" t="n">
-        <v>6867219</v>
+        <v>6867314</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127795216</v>
+        <v>127795817</v>
       </c>
       <c r="B9" t="n">
-        <v>79115</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469146</v>
+        <v>469179</v>
       </c>
       <c r="R9" t="n">
-        <v>6867271</v>
+        <v>6867255</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 999-2025 artfynd.xlsx
+++ b/artfynd/A 999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795120</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795216</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795594</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795776</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795470</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,8 +1498,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795817</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>